--- a/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664CD33B-1F5F-44DC-ABEC-360C2E908090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518D2A50-B79F-4542-9882-9831731A643B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34305" yWindow="4065" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35970" yWindow="3735" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -103,6 +103,30 @@
   </si>
   <si>
     <t>Luna, Luis Alejo Leonel</t>
+  </si>
+  <si>
+    <t>Sueldo, Celeste Micaela</t>
+  </si>
+  <si>
+    <t>Pizarro, Santiago</t>
+  </si>
+  <si>
+    <t>Soto, Mario</t>
+  </si>
+  <si>
+    <t>Vega, Emiliano</t>
+  </si>
+  <si>
+    <t>Ortiz, Víctor Santiago</t>
+  </si>
+  <si>
+    <t>Castro, Fidel Alejandro</t>
+  </si>
+  <si>
+    <t>Córdoba, Oscar</t>
+  </si>
+  <si>
+    <t>X2</t>
   </si>
 </sst>
 </file>
@@ -444,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F21"/>
+  <dimension ref="B2:F29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -617,6 +641,9 @@
       <c r="B15">
         <v>12</v>
       </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
@@ -631,6 +658,9 @@
       <c r="B16">
         <v>13</v>
       </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
       <c r="D16" t="s">
         <v>19</v>
       </c>
@@ -694,6 +724,94 @@
       </c>
       <c r="E21" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518D2A50-B79F-4542-9882-9831731A643B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815E136D-3AD1-4942-B977-E7EC5068A426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35970" yWindow="3735" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31440" yWindow="6960" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -127,6 +127,36 @@
   </si>
   <si>
     <t>X2</t>
+  </si>
+  <si>
+    <t>Tapia, Facundo</t>
+  </si>
+  <si>
+    <t>Molina, Claudio Daniel</t>
+  </si>
+  <si>
+    <t>Villagra, Danisa Aylen</t>
+  </si>
+  <si>
+    <t>Bernadó, Germán Andrés</t>
+  </si>
+  <si>
+    <t>Ramos Castillo, Florencia Anahí</t>
+  </si>
+  <si>
+    <t>Hizo funciones, y colocon onclick para invocarla a la función</t>
+  </si>
+  <si>
+    <t>Marón, Malena</t>
+  </si>
+  <si>
+    <t>Salas, María de los Angeles</t>
+  </si>
+  <si>
+    <t>Rodriguez, Mario Valentín</t>
+  </si>
+  <si>
+    <t>Casas, Cristian</t>
   </si>
 </sst>
 </file>
@@ -468,14 +498,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F29"/>
+  <dimension ref="B2:F38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
@@ -812,6 +842,111 @@
       </c>
       <c r="D29" t="s">
         <v>5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="D32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>33</v>
+      </c>
+      <c r="D36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>34</v>
+      </c>
+      <c r="D37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>35</v>
+      </c>
+      <c r="D38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815E136D-3AD1-4942-B977-E7EC5068A426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3466365C-87B7-4773-ABAC-8671263F80B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31440" yWindow="6960" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -157,6 +157,21 @@
   </si>
   <si>
     <t>Casas, Cristian</t>
+  </si>
+  <si>
+    <t>Lopez, María Fernanda</t>
+  </si>
+  <si>
+    <t>Salas, Luis Alberto</t>
+  </si>
+  <si>
+    <t>Gonzalez Pontífice, Angeles Lilian</t>
+  </si>
+  <si>
+    <t>Toloza, Laura Ivana</t>
+  </si>
+  <si>
+    <t>Nieva, Germán Andres</t>
   </si>
 </sst>
 </file>
@@ -498,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F38"/>
+  <dimension ref="B2:F43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -949,6 +964,61 @@
         <v>2</v>
       </c>
     </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>37</v>
+      </c>
+      <c r="D40" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>38</v>
+      </c>
+      <c r="D41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>40</v>
+      </c>
+      <c r="D43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>

--- a/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3466365C-87B7-4773-ABAC-8671263F80B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAECDC7-3E53-4B8C-947F-24997B32018C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="49">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -195,7 +195,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,6 +214,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -227,12 +233,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,17 +520,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F43"/>
+  <dimension ref="B2:G43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="54.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>18</v>
       </c>
@@ -531,8 +539,9 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
@@ -545,11 +554,12 @@
       <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -559,8 +569,11 @@
       <c r="E4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -570,8 +583,11 @@
       <c r="E5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -581,42 +597,51 @@
       <c r="E6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7">
+      <c r="F6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8">
+      <c r="F7" s="3">
+        <v>2</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
         <v>5</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>6</v>
       </c>
@@ -626,19 +651,25 @@
       <c r="E9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7</v>
       </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>8</v>
       </c>
@@ -648,8 +679,11 @@
       <c r="E11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>9</v>
       </c>
@@ -659,8 +693,11 @@
       <c r="E12" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10</v>
       </c>
@@ -670,8 +707,11 @@
       <c r="E13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>11</v>
       </c>
@@ -681,42 +721,51 @@
       <c r="E14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>12</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>13</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>14</v>
       </c>
@@ -726,8 +775,11 @@
       <c r="E17" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>15</v>
       </c>
@@ -737,8 +789,11 @@
       <c r="E18" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>16</v>
       </c>
@@ -748,8 +803,11 @@
       <c r="E19" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>17</v>
       </c>
@@ -759,8 +817,11 @@
       <c r="E20" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>18</v>
       </c>
@@ -770,8 +831,11 @@
       <c r="E21" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>19</v>
       </c>
@@ -781,8 +845,11 @@
       <c r="E22" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>20</v>
       </c>
@@ -792,8 +859,11 @@
       <c r="E23" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>21</v>
       </c>
@@ -803,8 +873,11 @@
       <c r="E24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>22</v>
       </c>
@@ -814,8 +887,11 @@
       <c r="E25" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>23</v>
       </c>
@@ -825,8 +901,11 @@
       <c r="E26" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>24</v>
       </c>
@@ -836,8 +915,11 @@
       <c r="E27" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>25</v>
       </c>
@@ -847,22 +929,29 @@
       <c r="E28" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29">
+      <c r="F28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="3">
         <v>26</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="3">
+        <v>2</v>
+      </c>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>27</v>
       </c>
@@ -872,8 +961,11 @@
       <c r="E30" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>28</v>
       </c>
@@ -883,8 +975,11 @@
       <c r="E31" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>29</v>
       </c>
@@ -894,8 +989,11 @@
       <c r="E32" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>30</v>
       </c>
@@ -905,8 +1003,11 @@
       <c r="E33" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>31</v>
       </c>
@@ -914,13 +1015,16 @@
         <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>2</v>
-      </c>
-      <c r="F34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>32</v>
       </c>
@@ -930,8 +1034,11 @@
       <c r="E35" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>33</v>
       </c>
@@ -941,8 +1048,11 @@
       <c r="E36" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>34</v>
       </c>
@@ -952,8 +1062,11 @@
       <c r="E37" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>35</v>
       </c>
@@ -963,8 +1076,11 @@
       <c r="E38" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>36</v>
       </c>
@@ -974,8 +1090,11 @@
       <c r="E39" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>37</v>
       </c>
@@ -985,8 +1104,11 @@
       <c r="E40" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>38</v>
       </c>
@@ -996,8 +1118,11 @@
       <c r="E41" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>39</v>
       </c>
@@ -1007,8 +1132,11 @@
       <c r="E42" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>40</v>
       </c>
@@ -1018,10 +1146,13 @@
       <c r="E43" t="s">
         <v>2</v>
       </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAECDC7-3E53-4B8C-947F-24997B32018C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11C6E87-EB32-47B2-9DCC-B51418F6EC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32415" yWindow="3285" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="61">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -172,6 +172,42 @@
   </si>
   <si>
     <t>Nieva, Germán Andres</t>
+  </si>
+  <si>
+    <t>Fernandez, Daniel Agustín</t>
+  </si>
+  <si>
+    <t>Cano Campos, Juan Andrés</t>
+  </si>
+  <si>
+    <t>Maita, Daiana Macarena</t>
+  </si>
+  <si>
+    <t>Castro Leiva, Noelia Estefanía</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Utilizó IA para resolver todo el proyecto</t>
+  </si>
+  <si>
+    <t>Calas, Juan Pablo</t>
+  </si>
+  <si>
+    <t>Andreata, Lucas Daniel</t>
+  </si>
+  <si>
+    <t>Villega, Daniel Andres</t>
+  </si>
+  <si>
+    <t>Monge, Jorge David</t>
+  </si>
+  <si>
+    <t>Maltese, Pablo David</t>
+  </si>
+  <si>
+    <t>Bazán, Oscar Alfredo</t>
   </si>
 </sst>
 </file>
@@ -195,7 +231,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -220,6 +256,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3DBFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -233,13 +275,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G43"/>
+  <dimension ref="B2:G53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -532,14 +575,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -602,42 +645,42 @@
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="3">
-        <v>2</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="3">
-        <v>2</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -729,19 +772,19 @@
       <c r="B15">
         <v>12</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="3">
-        <v>2</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="F15" s="2">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -749,19 +792,19 @@
       <c r="B16">
         <v>13</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="3">
-        <v>2</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -934,22 +977,22 @@
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>26</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F29" s="3">
-        <v>2</v>
-      </c>
-      <c r="G29" s="3"/>
+      <c r="F29" s="2">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30">
@@ -1008,19 +1051,20 @@
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34">
+      <c r="B34" s="4">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
+      <c r="C34" s="4"/>
+      <c r="D34" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F34">
-        <v>2</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="F34" s="4">
+        <v>2</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1147,6 +1191,152 @@
         <v>2</v>
       </c>
       <c r="F43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>42</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>43</v>
+      </c>
+      <c r="D46" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="4">
+        <v>44</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="4">
+        <v>2</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>45</v>
+      </c>
+      <c r="D48" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>46</v>
+      </c>
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>47</v>
+      </c>
+      <c r="D50" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>48</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>49</v>
+      </c>
+      <c r="D52" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>50</v>
+      </c>
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53">
         <v>8</v>
       </c>
     </row>

--- a/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11C6E87-EB32-47B2-9DCC-B51418F6EC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2417132C-ACDA-4334-81F0-6FBC39CDBE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32415" yWindow="3285" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30855" yWindow="3705" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -208,6 +208,21 @@
   </si>
   <si>
     <t>Bazán, Oscar Alfredo</t>
+  </si>
+  <si>
+    <t>Herrera, Mario Alberto</t>
+  </si>
+  <si>
+    <t>Maidana, Alejo Leonel</t>
+  </si>
+  <si>
+    <t>Monges, Braian</t>
+  </si>
+  <si>
+    <t>Cirione Leguizamon, Erik Mirko</t>
+  </si>
+  <si>
+    <t>Cano, Marcelo Emanuel</t>
   </si>
 </sst>
 </file>
@@ -279,10 +294,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G53"/>
+  <dimension ref="B2:G58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -575,14 +590,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -1051,20 +1066,20 @@
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="4">
+      <c r="B34" s="3">
         <v>31</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4" t="s">
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F34" s="4">
-        <v>2</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="F34" s="3">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1237,22 +1252,22 @@
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="4">
+      <c r="B47" s="3">
         <v>44</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="4">
-        <v>2</v>
-      </c>
-      <c r="G47" s="4" t="s">
+      <c r="F47" s="3">
+        <v>2</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1337,6 +1352,76 @@
         <v>2</v>
       </c>
       <c r="F53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>51</v>
+      </c>
+      <c r="D54" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>52</v>
+      </c>
+      <c r="D55" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>53</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>54</v>
+      </c>
+      <c r="D57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>55</v>
+      </c>
+      <c r="D58" t="s">
+        <v>65</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58">
         <v>8</v>
       </c>
     </row>

--- a/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2417132C-ACDA-4334-81F0-6FBC39CDBE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4A3C5F-273F-4C8B-9B9B-F6CD8E836CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="3705" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="72">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -223,6 +223,24 @@
   </si>
   <si>
     <t>Cano, Marcelo Emanuel</t>
+  </si>
+  <si>
+    <t>Varela Oliva, Irma Celina</t>
+  </si>
+  <si>
+    <t>Veliz, Fabricio Damian</t>
+  </si>
+  <si>
+    <t>Diaz, Felipe Luis</t>
+  </si>
+  <si>
+    <t>Casas, Victoria Agustina</t>
+  </si>
+  <si>
+    <t>Arias, Enzo</t>
+  </si>
+  <si>
+    <t>Castillo, Fernando Nicolás</t>
   </si>
 </sst>
 </file>
@@ -578,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G58"/>
+  <dimension ref="B2:G64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1425,6 +1443,90 @@
         <v>8</v>
       </c>
     </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>56</v>
+      </c>
+      <c r="D59" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>57</v>
+      </c>
+      <c r="D60" t="s">
+        <v>67</v>
+      </c>
+      <c r="E60" t="s">
+        <v>2</v>
+      </c>
+      <c r="F60">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>58</v>
+      </c>
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>59</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>60</v>
+      </c>
+      <c r="D63" t="s">
+        <v>70</v>
+      </c>
+      <c r="E63" t="s">
+        <v>6</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>61</v>
+      </c>
+      <c r="D64" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64" t="s">
+        <v>2</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>

--- a/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohorte06_TP01/Cohoorte06.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel M\Desktop\Modulo02_JavaScript\00000_Correcciones\Cohorte06_TP01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4A3C5F-273F-4C8B-9B9B-F6CD8E836CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="75">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -241,12 +240,21 @@
   </si>
   <si>
     <t>Castillo, Fernando Nicolás</t>
+  </si>
+  <si>
+    <t>Galarza, Malena Yael</t>
+  </si>
+  <si>
+    <t>Isasmendi, Saul Abraham</t>
+  </si>
+  <si>
+    <t>Latorre Mejía, Marlene</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -595,8 +603,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:G67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1527,6 +1535,48 @@
         <v>8</v>
       </c>
     </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>62</v>
+      </c>
+      <c r="D65" t="s">
+        <v>72</v>
+      </c>
+      <c r="E65" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>63</v>
+      </c>
+      <c r="D66" t="s">
+        <v>73</v>
+      </c>
+      <c r="E66" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>64</v>
+      </c>
+      <c r="D67" t="s">
+        <v>74</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
